--- a/Ciclo 02 - 2026/CalendarioEvaluaciones.xlsx
+++ b/Ciclo 02 - 2026/CalendarioEvaluaciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\Ciclo 02 - 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F997177-9F62-4698-9DCD-1449BDFC506A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F2AC4CB-2E10-4E3D-ACB4-39BF85B8F6E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$1:$I$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$J$46</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$J$39</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="58">
   <si>
     <t>Materia</t>
   </si>
@@ -191,6 +191,30 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>Desafio Practico 1</t>
+  </si>
+  <si>
+    <t>U4,5,6</t>
+  </si>
+  <si>
+    <t>Desafio Practico 2</t>
+  </si>
+  <si>
+    <t>Desafio Practico 3</t>
+  </si>
+  <si>
+    <t>Desafio Practico 4</t>
+  </si>
+  <si>
+    <t>Curso Huawei</t>
+  </si>
+  <si>
+    <t>U1,2,3,4,5</t>
+  </si>
+  <si>
+    <t>Todas</t>
   </si>
 </sst>
 </file>
@@ -202,7 +226,7 @@
     <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -261,13 +285,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="20"/>
       <color theme="1"/>
@@ -290,8 +307,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -328,8 +361,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -352,12 +391,190 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -391,12 +608,12 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -406,16 +623,13 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -432,30 +646,137 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -688,7 +1009,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -701,12 +1022,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -720,7 +1035,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="12"/>
+        <sz val="14"/>
         <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
@@ -733,7 +1048,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -746,12 +1061,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -817,10 +1126,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2365A705-3F72-4A55-B46A-AA1E8BBAB0F9}" name="Tabla1" displayName="Tabla1" ref="B1:H42" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="B1:H42" xr:uid="{2365A705-3F72-4A55-B46A-AA1E8BBAB0F9}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:H42">
-    <sortCondition ref="E1:E42"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2365A705-3F72-4A55-B46A-AA1E8BBAB0F9}" name="Tabla1" displayName="Tabla1" ref="B1:H35" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="B1:H35" xr:uid="{2365A705-3F72-4A55-B46A-AA1E8BBAB0F9}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:H35">
+    <sortCondition ref="E1:E35"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{331E2AD1-F1B3-4D28-A2FE-E01CDD07D79C}" name="Materia" dataDxfId="6"/>
@@ -1101,7 +1410,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:O45"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="26.25" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="2"/>
@@ -1117,7 +1426,7 @@
     <col min="11" max="16384" width="9.28515625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" s="1" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1141,764 +1450,774 @@
       </c>
       <c r="J1" s="13"/>
     </row>
-    <row r="2" spans="2:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="36" t="s">
+    <row r="2" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="77"/>
+      <c r="B2" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="27">
+      <c r="D2" s="43">
         <v>0.2</v>
       </c>
-      <c r="E2" s="28">
+      <c r="E2" s="44">
         <v>46242</v>
       </c>
-      <c r="F2" s="29">
+      <c r="F2" s="45">
         <v>46264</v>
       </c>
-      <c r="G2" s="30"/>
-      <c r="H2" s="31" t="s">
+      <c r="G2" s="46"/>
+      <c r="H2" s="47" t="s">
         <v>28</v>
       </c>
       <c r="J2" s="16"/>
     </row>
-    <row r="3" spans="2:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="35" t="s">
+    <row r="3" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="51">
         <v>0.2</v>
       </c>
-      <c r="E3" s="28">
+      <c r="E3" s="52">
         <v>46246</v>
       </c>
-      <c r="F3" s="29"/>
-      <c r="G3" s="30">
+      <c r="F3" s="53"/>
+      <c r="G3" s="54">
         <v>0.99930555555555556</v>
       </c>
-      <c r="H3" s="31" t="s">
+      <c r="H3" s="55" t="s">
         <v>15</v>
       </c>
       <c r="J3" s="16"/>
     </row>
-    <row r="4" spans="2:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="36" t="s">
+    <row r="4" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B4" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="58">
         <v>0.15</v>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="59">
         <v>46249</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="60">
         <v>46292</v>
       </c>
-      <c r="G4" s="30"/>
-      <c r="H4" s="31" t="s">
+      <c r="G4" s="61"/>
+      <c r="H4" s="62" t="s">
         <v>26</v>
       </c>
       <c r="J4" s="16"/>
     </row>
-    <row r="5" spans="2:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="37" t="s">
+    <row r="5" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="51">
         <v>0.1</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="52">
         <v>46251</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="53">
         <v>46257</v>
       </c>
-      <c r="G5" s="30"/>
-      <c r="H5" s="31" t="s">
+      <c r="G5" s="54"/>
+      <c r="H5" s="55" t="s">
         <v>15</v>
       </c>
       <c r="J5" s="16"/>
     </row>
-    <row r="6" spans="2:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="39" t="s">
+    <row r="6" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="26">
         <v>0.1</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="27">
         <v>46251</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="28">
         <v>46257</v>
       </c>
-      <c r="G6" s="30"/>
-      <c r="H6" s="31"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="65"/>
       <c r="J6" s="16"/>
     </row>
-    <row r="7" spans="2:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="37" t="s">
+    <row r="7" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B7" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="58">
+        <v>0.1</v>
+      </c>
+      <c r="E7" s="67">
+        <v>46253</v>
+      </c>
+      <c r="F7" s="60"/>
+      <c r="G7" s="61">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H7" s="62" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="16"/>
+    </row>
+    <row r="8" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B8" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C8" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D8" s="43">
         <v>0.1</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E8" s="44">
         <v>46266</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F8" s="45">
         <v>46353</v>
       </c>
-      <c r="G7" s="30"/>
-      <c r="H7" s="31"/>
-      <c r="J7" s="16"/>
-    </row>
-    <row r="8" spans="2:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="37" t="s">
+      <c r="G8" s="46"/>
+      <c r="H8" s="47"/>
+      <c r="J8" s="16"/>
+    </row>
+    <row r="9" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C9" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D9" s="51">
         <v>0.15</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E9" s="52">
         <v>46272</v>
       </c>
-      <c r="F8" s="29"/>
-      <c r="G8" s="30">
+      <c r="F9" s="53"/>
+      <c r="G9" s="54">
         <v>0.875</v>
       </c>
-      <c r="H8" s="31" t="s">
+      <c r="H9" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="J8" s="16"/>
-    </row>
-    <row r="9" spans="2:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="39" t="s">
+      <c r="J9" s="16"/>
+    </row>
+    <row r="10" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C10" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D10" s="26">
         <v>0.15</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E10" s="27">
         <v>46272</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F10" s="28">
         <v>46278</v>
       </c>
-      <c r="G9" s="30"/>
-      <c r="H9" s="31"/>
-      <c r="J9" s="16"/>
-    </row>
-    <row r="10" spans="2:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="35" t="s">
+      <c r="G10" s="29"/>
+      <c r="H10" s="65"/>
+      <c r="J10" s="16"/>
+    </row>
+    <row r="11" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C11" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D11" s="26">
         <v>0.1</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E11" s="27">
         <v>46274</v>
       </c>
-      <c r="F10" s="29"/>
-      <c r="G10" s="30">
+      <c r="F11" s="28"/>
+      <c r="G11" s="29">
         <v>0.875</v>
       </c>
-      <c r="H10" s="31" t="s">
+      <c r="H11" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="J10" s="16"/>
-    </row>
-    <row r="11" spans="2:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="37" t="s">
+      <c r="J11" s="16"/>
+    </row>
+    <row r="12" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B12" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="57" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="58">
+        <v>0.15</v>
+      </c>
+      <c r="E12" s="67">
+        <v>46274</v>
+      </c>
+      <c r="F12" s="60"/>
+      <c r="G12" s="61">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H12" s="62" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" s="16"/>
+    </row>
+    <row r="13" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="77"/>
+      <c r="B13" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C13" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D13" s="43">
         <v>0.1</v>
       </c>
-      <c r="E11" s="28">
+      <c r="E13" s="44">
         <v>46279</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F13" s="45">
         <v>46285</v>
       </c>
-      <c r="G11" s="30"/>
-      <c r="H11" s="31" t="s">
+      <c r="G13" s="46"/>
+      <c r="H13" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="J11" s="16"/>
-    </row>
-    <row r="12" spans="2:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="39" t="s">
+      <c r="J13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B14" s="70" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="51">
+        <v>0.1</v>
+      </c>
+      <c r="E14" s="71">
+        <v>46288</v>
+      </c>
+      <c r="F14" s="53"/>
+      <c r="G14" s="54">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H14" s="55" t="s">
+        <v>28</v>
+      </c>
+      <c r="J14" s="20"/>
+    </row>
+    <row r="15" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B15" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C15" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D15" s="58">
         <v>0.1</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E15" s="59">
         <v>46290</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F15" s="60">
         <v>46297</v>
       </c>
-      <c r="G12" s="30"/>
-      <c r="H12" s="31"/>
-      <c r="J12" s="16"/>
-    </row>
-    <row r="13" spans="2:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="35" t="s">
+      <c r="G15" s="61"/>
+      <c r="H15" s="62"/>
+      <c r="J15" s="20"/>
+    </row>
+    <row r="16" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C16" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D16" s="51">
         <v>0.2</v>
       </c>
-      <c r="E13" s="28">
+      <c r="E16" s="52">
         <v>46295</v>
       </c>
-      <c r="F13" s="29"/>
-      <c r="G13" s="30">
+      <c r="F16" s="53"/>
+      <c r="G16" s="54">
         <v>0.875</v>
       </c>
-      <c r="H13" s="31" t="s">
+      <c r="H16" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="J13" s="20"/>
-    </row>
-    <row r="14" spans="2:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="36" t="s">
+      <c r="J16" s="20"/>
+    </row>
+    <row r="17" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B17" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C17" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D17" s="58">
         <v>0.3</v>
       </c>
-      <c r="E14" s="28">
+      <c r="E17" s="59">
         <v>46297</v>
       </c>
-      <c r="F14" s="29"/>
-      <c r="G14" s="30">
+      <c r="F17" s="60"/>
+      <c r="G17" s="61">
         <v>0.875</v>
       </c>
-      <c r="H14" s="31" t="s">
+      <c r="H17" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="J14" s="20"/>
-    </row>
-    <row r="15" spans="2:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="39" t="s">
+      <c r="J17" s="20"/>
+    </row>
+    <row r="18" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="77"/>
+      <c r="B18" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C18" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D18" s="51">
         <v>0.2</v>
       </c>
-      <c r="E15" s="28">
+      <c r="E18" s="52">
         <v>46300</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F18" s="53">
         <v>46320</v>
       </c>
-      <c r="G15" s="30"/>
-      <c r="H15" s="31"/>
-      <c r="J15" s="20"/>
-    </row>
-    <row r="16" spans="2:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="37" t="s">
+      <c r="G18" s="54"/>
+      <c r="H18" s="55"/>
+      <c r="J18" s="21"/>
+    </row>
+    <row r="19" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="77"/>
+      <c r="B19" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="57" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="74">
+        <v>0.1</v>
+      </c>
+      <c r="E19" s="59">
+        <v>46302</v>
+      </c>
+      <c r="F19" s="60"/>
+      <c r="G19" s="61">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H19" s="62" t="s">
+        <v>26</v>
+      </c>
+      <c r="J19" s="21"/>
+    </row>
+    <row r="20" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B20" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C20" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D20" s="51">
         <v>0.1</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E20" s="52">
         <v>46308</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F20" s="53">
         <v>46313</v>
       </c>
-      <c r="G16" s="30"/>
-      <c r="H16" s="31" t="s">
+      <c r="G20" s="54"/>
+      <c r="H20" s="55" t="s">
         <v>38</v>
       </c>
-      <c r="J16" s="20"/>
-    </row>
-    <row r="17" spans="2:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="36" t="s">
+      <c r="J20" s="20"/>
+    </row>
+    <row r="21" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B21" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C21" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D21" s="58">
         <v>0.15</v>
       </c>
-      <c r="E17" s="28">
+      <c r="E21" s="59">
         <v>46308</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F21" s="60">
         <v>46327</v>
       </c>
-      <c r="G17" s="30"/>
-      <c r="H17" s="31" t="s">
+      <c r="G21" s="61"/>
+      <c r="H21" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="J17" s="20"/>
-    </row>
-    <row r="18" spans="2:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="36" t="s">
+      <c r="J21" s="21"/>
+    </row>
+    <row r="22" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B22" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C22" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="27">
+      <c r="D22" s="51">
         <v>0.2</v>
       </c>
-      <c r="E18" s="28">
+      <c r="E22" s="52">
         <v>46315</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F22" s="53">
         <v>46344</v>
       </c>
-      <c r="G18" s="30"/>
-      <c r="H18" s="31" t="s">
+      <c r="G22" s="54"/>
+      <c r="H22" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="J18" s="21"/>
-    </row>
-    <row r="19" spans="2:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="35" t="s">
+      <c r="J22" s="21"/>
+    </row>
+    <row r="23" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B23" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="57" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="58">
+        <v>0.1</v>
+      </c>
+      <c r="E23" s="59">
+        <v>46316</v>
+      </c>
+      <c r="F23" s="60"/>
+      <c r="G23" s="61">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H23" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="J23" s="21"/>
+    </row>
+    <row r="24" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="77"/>
+      <c r="B24" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="26" t="s">
+      <c r="C24" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="27">
+      <c r="D24" s="51">
         <v>0.1</v>
       </c>
-      <c r="E19" s="28">
+      <c r="E24" s="52">
         <v>46323</v>
       </c>
-      <c r="F19" s="29"/>
-      <c r="G19" s="30">
+      <c r="F24" s="53"/>
+      <c r="G24" s="54">
         <v>0.875</v>
       </c>
-      <c r="H19" s="31" t="s">
+      <c r="H24" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="J19" s="21"/>
-    </row>
-    <row r="20" spans="2:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="39" t="s">
+      <c r="J24" s="21"/>
+    </row>
+    <row r="25" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="77"/>
+      <c r="B25" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C25" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="27">
+      <c r="D25" s="58">
         <v>0.2</v>
       </c>
-      <c r="E20" s="28">
+      <c r="E25" s="59">
         <v>46325</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F25" s="60">
         <v>46341</v>
       </c>
-      <c r="G20" s="30"/>
-      <c r="H20" s="31"/>
-      <c r="J20" s="20"/>
-    </row>
-    <row r="21" spans="2:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="37" t="s">
+      <c r="G25" s="61"/>
+      <c r="H25" s="62"/>
+      <c r="J25" s="21"/>
+    </row>
+    <row r="26" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B26" s="76" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="43">
+        <v>0.15</v>
+      </c>
+      <c r="E26" s="44">
+        <v>46330</v>
+      </c>
+      <c r="F26" s="45"/>
+      <c r="G26" s="46">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H26" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="J26" s="21"/>
+    </row>
+    <row r="27" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B27" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="C27" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D27" s="51">
         <v>0.1</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E27" s="52">
         <v>46335</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F27" s="53">
         <v>46341</v>
       </c>
-      <c r="G21" s="30"/>
-      <c r="H21" s="31" t="s">
+      <c r="G27" s="54"/>
+      <c r="H27" s="55" t="s">
         <v>39</v>
-      </c>
-      <c r="J21" s="21"/>
-    </row>
-    <row r="22" spans="2:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" s="27">
-        <v>0.2</v>
-      </c>
-      <c r="E22" s="28">
-        <v>46336</v>
-      </c>
-      <c r="F22" s="29"/>
-      <c r="G22" s="30">
-        <v>0.49930555555555556</v>
-      </c>
-      <c r="H22" s="31"/>
-      <c r="J22" s="21"/>
-    </row>
-    <row r="23" spans="2:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="27">
-        <v>0.2</v>
-      </c>
-      <c r="E23" s="28">
-        <v>46336</v>
-      </c>
-      <c r="F23" s="29"/>
-      <c r="G23" s="30">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H23" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="J23" s="21"/>
-    </row>
-    <row r="24" spans="2:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="27">
-        <v>0.15</v>
-      </c>
-      <c r="E24" s="28">
-        <v>46342</v>
-      </c>
-      <c r="F24" s="29"/>
-      <c r="G24" s="30">
-        <v>0.875</v>
-      </c>
-      <c r="H24" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="J24" s="21"/>
-    </row>
-    <row r="25" spans="2:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="E25" s="28">
-        <v>46342</v>
-      </c>
-      <c r="F25" s="29">
-        <v>46343</v>
-      </c>
-      <c r="G25" s="30"/>
-      <c r="H25" s="31"/>
-      <c r="J25" s="21"/>
-    </row>
-    <row r="26" spans="2:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="27">
-        <v>0.2</v>
-      </c>
-      <c r="E26" s="28">
-        <v>46344</v>
-      </c>
-      <c r="F26" s="29"/>
-      <c r="G26" s="30">
-        <v>0.875</v>
-      </c>
-      <c r="H26" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="J26" s="21"/>
-    </row>
-    <row r="27" spans="2:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="D27" s="27">
-        <v>0.2</v>
-      </c>
-      <c r="E27" s="28">
-        <v>46349</v>
-      </c>
-      <c r="F27" s="29"/>
-      <c r="G27" s="30">
-        <v>0.875</v>
-      </c>
-      <c r="H27" s="31" t="s">
-        <v>41</v>
       </c>
       <c r="K27" s="16"/>
       <c r="L27" s="16"/>
     </row>
-    <row r="28" spans="2:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" s="26"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="31"/>
+    <row r="28" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B28" s="69" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="26">
+        <v>0.2</v>
+      </c>
+      <c r="E28" s="27">
+        <v>46336</v>
+      </c>
+      <c r="F28" s="28"/>
+      <c r="G28" s="29">
+        <v>0.49930555555555556</v>
+      </c>
+      <c r="H28" s="65"/>
       <c r="J28" s="16"/>
       <c r="K28" s="16"/>
       <c r="L28" s="16"/>
     </row>
-    <row r="29" spans="2:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" s="26"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="31"/>
+    <row r="29" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B29" s="72" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="57" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="58">
+        <v>0.2</v>
+      </c>
+      <c r="E29" s="59">
+        <v>46336</v>
+      </c>
+      <c r="F29" s="60"/>
+      <c r="G29" s="61">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H29" s="62" t="s">
+        <v>41</v>
+      </c>
       <c r="J29" s="16"/>
       <c r="K29" s="16"/>
       <c r="L29" s="16"/>
     </row>
-    <row r="30" spans="2:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" s="26"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="30"/>
-      <c r="H30" s="31"/>
+    <row r="30" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="77"/>
+      <c r="B30" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="51">
+        <v>0.15</v>
+      </c>
+      <c r="E30" s="52">
+        <v>46342</v>
+      </c>
+      <c r="F30" s="53"/>
+      <c r="G30" s="54">
+        <v>0.875</v>
+      </c>
+      <c r="H30" s="55" t="s">
+        <v>31</v>
+      </c>
       <c r="J30" s="21"/>
       <c r="K30" s="21"/>
       <c r="L30" s="21"/>
     </row>
-    <row r="31" spans="2:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C31" s="26"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="30"/>
-      <c r="H31" s="31"/>
+    <row r="31" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="77"/>
+      <c r="B31" s="64" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="D31" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="E31" s="27">
+        <v>46342</v>
+      </c>
+      <c r="F31" s="28">
+        <v>46343</v>
+      </c>
+      <c r="G31" s="29"/>
+      <c r="H31" s="65"/>
       <c r="J31" s="21"/>
       <c r="K31" s="21"/>
       <c r="L31" s="21"/>
     </row>
-    <row r="32" spans="2:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C32" s="26"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="31"/>
+    <row r="32" spans="1:13" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="77"/>
+      <c r="B32" s="69" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="26">
+        <v>0.2</v>
+      </c>
+      <c r="E32" s="27">
+        <v>46344</v>
+      </c>
+      <c r="F32" s="28"/>
+      <c r="G32" s="29">
+        <v>0.875</v>
+      </c>
+      <c r="H32" s="65" t="s">
+        <v>20</v>
+      </c>
       <c r="K32" s="21"/>
       <c r="L32" s="21"/>
       <c r="M32" s="22"/>
     </row>
-    <row r="33" spans="2:15" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="25" t="s">
+    <row r="33" spans="1:12" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="77"/>
+      <c r="B33" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="C33" s="26"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="31"/>
+      <c r="C33" s="57" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33" s="58">
+        <v>0.2</v>
+      </c>
+      <c r="E33" s="67">
+        <v>46344</v>
+      </c>
+      <c r="F33" s="60"/>
+      <c r="G33" s="61">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H33" s="62" t="s">
+        <v>57</v>
+      </c>
       <c r="K33" s="21"/>
       <c r="L33" s="21"/>
     </row>
-    <row r="34" spans="2:15" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="25"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="29"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="31"/>
+    <row r="34" spans="1:12" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B34" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="E34" s="37">
+        <v>46349</v>
+      </c>
+      <c r="F34" s="38"/>
+      <c r="G34" s="39">
+        <v>0.875</v>
+      </c>
+      <c r="H34" s="40" t="s">
+        <v>41</v>
+      </c>
       <c r="K34" s="21"/>
       <c r="L34" s="21"/>
     </row>
-    <row r="35" spans="2:15" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="25"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="27"/>
-      <c r="E35" s="33"/>
-      <c r="F35" s="29"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="31"/>
+    <row r="35" spans="1:12" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B35" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" s="32">
+        <v>0.1</v>
+      </c>
+      <c r="E35" s="31"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="30"/>
       <c r="J35" s="21"/>
       <c r="L35" s="21"/>
     </row>
-    <row r="36" spans="2:15" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="25"/>
-      <c r="C36" s="26"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="29"/>
-      <c r="G36" s="30"/>
-      <c r="H36" s="31"/>
-      <c r="J36" s="21"/>
-      <c r="L36" s="21"/>
-    </row>
-    <row r="37" spans="2:15" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="25"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="31"/>
-      <c r="J37" s="21"/>
-      <c r="L37" s="21"/>
-      <c r="O37" s="22"/>
-    </row>
-    <row r="38" spans="2:15" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="25"/>
-      <c r="C38" s="26"/>
-      <c r="D38" s="27"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="29"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="31"/>
-      <c r="J38" s="16"/>
-      <c r="L38" s="16"/>
-    </row>
-    <row r="39" spans="2:15" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B39" s="25"/>
-      <c r="C39" s="26"/>
-      <c r="D39" s="27"/>
-      <c r="E39" s="28"/>
-      <c r="F39" s="29"/>
-      <c r="G39" s="30"/>
-      <c r="H39" s="31"/>
-      <c r="J39" s="16"/>
-      <c r="M39" s="16"/>
-    </row>
-    <row r="40" spans="2:15" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="25"/>
-      <c r="C40" s="26"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="31"/>
-      <c r="J40" s="16"/>
-      <c r="M40" s="16"/>
-    </row>
-    <row r="41" spans="2:15" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="25"/>
-      <c r="C41" s="26"/>
-      <c r="D41" s="27"/>
-      <c r="E41" s="28"/>
-      <c r="F41" s="29"/>
-      <c r="G41" s="30"/>
-      <c r="H41" s="31"/>
-      <c r="J41" s="16"/>
-      <c r="M41" s="16"/>
-    </row>
-    <row r="42" spans="2:15" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="25"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="27"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="29"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="31"/>
-      <c r="J42" s="16"/>
-      <c r="M42" s="16"/>
-    </row>
-    <row r="43" spans="2:15" s="15" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B43" s="23"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="24"/>
-      <c r="J43" s="16"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="B45" s="3"/>
+    <row r="36" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="23"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="24"/>
+      <c r="J36" s="16"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B37" s="3"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="B38" s="3"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:I42">
-    <sortCondition ref="E2:E42"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:I35">
+    <sortCondition ref="E2:E35"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Ciclo 02 - 2026/CalendarioEvaluaciones.xlsx
+++ b/Ciclo 02 - 2026/CalendarioEvaluaciones.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\Ciclo 02 - 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F2AC4CB-2E10-4E3D-ACB4-39BF85B8F6E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981FDE1F-C1B5-4C8E-80B1-4294A9E63E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$1:$I$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$J$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$I$39</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="75">
   <si>
     <t>Materia</t>
   </si>
@@ -215,6 +216,57 @@
   </si>
   <si>
     <t>Todas</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>LUNES</t>
+  </si>
+  <si>
+    <t>MARTES</t>
+  </si>
+  <si>
+    <t>MIERCOLES</t>
+  </si>
+  <si>
+    <t>JUEVES</t>
+  </si>
+  <si>
+    <t>VIERNES</t>
+  </si>
+  <si>
+    <t>Comunicación y Literatura</t>
+  </si>
+  <si>
+    <t>Ciudadania y Valores</t>
+  </si>
+  <si>
+    <t>Numeros y Formas</t>
+  </si>
+  <si>
+    <t>Ciencia y Tecnologia</t>
+  </si>
+  <si>
+    <t>Ingles</t>
+  </si>
+  <si>
+    <t>Ciencias de la Computacion</t>
+  </si>
+  <si>
+    <t>Numeros y Forma</t>
+  </si>
+  <si>
+    <t>Educacion Cristiana</t>
+  </si>
+  <si>
+    <t>Desarrollo Corporal</t>
+  </si>
+  <si>
+    <t>Artes</t>
+  </si>
+  <si>
+    <t>Devocional</t>
   </si>
 </sst>
 </file>
@@ -226,7 +278,7 @@
     <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -323,8 +375,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -367,8 +435,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9A57CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -569,12 +661,90 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -777,6 +947,78 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1123,6 +1365,99 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>427935</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>124238</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>82826</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>225387</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{163161D7-AE36-4FF2-9F72-0216971312D6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2098261" y="11623260"/>
+          <a:ext cx="7992717" cy="4408105"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>593586</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>110436</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>124238</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>169368</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7336522F-B1B1-4C79-B953-5B9C6E7D0693}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="593586" y="9290327"/>
+          <a:ext cx="11305761" cy="2378063"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1426,7 +1761,7 @@
     <col min="11" max="16384" width="9.28515625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="1" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1450,7 +1785,7 @@
       </c>
       <c r="J1" s="13"/>
     </row>
-    <row r="2" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="77"/>
       <c r="B2" s="41" t="s">
         <v>14</v>
@@ -1473,7 +1808,7 @@
       </c>
       <c r="J2" s="16"/>
     </row>
-    <row r="3" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="49" t="s">
         <v>11</v>
       </c>
@@ -1495,7 +1830,7 @@
       </c>
       <c r="J3" s="16"/>
     </row>
-    <row r="4" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="56" t="s">
         <v>14</v>
       </c>
@@ -1517,7 +1852,7 @@
       </c>
       <c r="J4" s="16"/>
     </row>
-    <row r="5" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="63" t="s">
         <v>12</v>
       </c>
@@ -1539,7 +1874,7 @@
       </c>
       <c r="J5" s="16"/>
     </row>
-    <row r="6" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="64" t="s">
         <v>42</v>
       </c>
@@ -1559,7 +1894,7 @@
       <c r="H6" s="65"/>
       <c r="J6" s="16"/>
     </row>
-    <row r="7" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B7" s="66" t="s">
         <v>13</v>
       </c>
@@ -1581,7 +1916,7 @@
       </c>
       <c r="J7" s="16"/>
     </row>
-    <row r="8" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B8" s="68" t="s">
         <v>12</v>
       </c>
@@ -1600,8 +1935,11 @@
       <c r="G8" s="46"/>
       <c r="H8" s="47"/>
       <c r="J8" s="16"/>
-    </row>
-    <row r="9" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="K8" s="15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="63" t="s">
         <v>12</v>
       </c>
@@ -1623,7 +1961,7 @@
       </c>
       <c r="J9" s="16"/>
     </row>
-    <row r="10" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="64" t="s">
         <v>42</v>
       </c>
@@ -1643,7 +1981,7 @@
       <c r="H10" s="65"/>
       <c r="J10" s="16"/>
     </row>
-    <row r="11" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="69" t="s">
         <v>11</v>
       </c>
@@ -1665,7 +2003,7 @@
       </c>
       <c r="J11" s="16"/>
     </row>
-    <row r="12" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B12" s="66" t="s">
         <v>13</v>
       </c>
@@ -1687,7 +2025,7 @@
       </c>
       <c r="J12" s="16"/>
     </row>
-    <row r="13" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="77"/>
       <c r="B13" s="68" t="s">
         <v>12</v>
@@ -1710,7 +2048,7 @@
       </c>
       <c r="J13" s="20"/>
     </row>
-    <row r="14" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="70" t="s">
         <v>13</v>
       </c>
@@ -1732,7 +2070,7 @@
       </c>
       <c r="J14" s="20"/>
     </row>
-    <row r="15" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B15" s="72" t="s">
         <v>42</v>
       </c>
@@ -1752,7 +2090,7 @@
       <c r="H15" s="62"/>
       <c r="J15" s="20"/>
     </row>
-    <row r="16" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="49" t="s">
         <v>11</v>
       </c>
@@ -2220,10 +2558,148 @@
     <sortCondition ref="E2:E35"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="55" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.35" header="0.3" footer="0.17"/>
+  <pageSetup scale="54" orientation="portrait" r:id="rId1"/>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="9" max="38" man="1"/>
+  </colBreaks>
+  <drawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50A4DFEF-9CFA-41F9-A8B9-C136CDE44FC9}">
+  <dimension ref="B1:F8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="6" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="78" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="78" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="91" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="78" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" s="78" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="79" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="88" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="93" t="s">
+        <v>66</v>
+      </c>
+      <c r="E3" s="95" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" s="96" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="82" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="89" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="94" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" s="90" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" s="101" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="99" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="92" t="s">
+        <v>72</v>
+      </c>
+      <c r="E5" s="93" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" s="86" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="80" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="100" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="84" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="94" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="87" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="97" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="81" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="79" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="83" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" s="83" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="98" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="84" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="82" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" s="84" t="s">
+        <v>74</v>
+      </c>
+      <c r="F8" s="85" t="s">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Ciclo 02 - 2026/CalendarioEvaluaciones.xlsx
+++ b/Ciclo 02 - 2026/CalendarioEvaluaciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\Ciclo 02 - 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981FDE1F-C1B5-4C8E-80B1-4294A9E63E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{947F4BE0-D542-432A-B53C-C2CBAEE37E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="74">
   <si>
     <t>Materia</t>
   </si>
@@ -216,9 +216,6 @@
   </si>
   <si>
     <t>Todas</t>
-  </si>
-  <si>
-    <t>P</t>
   </si>
   <si>
     <t>LUNES</t>
@@ -744,7 +741,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1019,6 +1016,27 @@
     <xf numFmtId="0" fontId="14" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="8" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1761,7 +1779,7 @@
     <col min="11" max="16384" width="9.28515625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1785,7 +1803,7 @@
       </c>
       <c r="J1" s="13"/>
     </row>
-    <row r="2" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="77"/>
       <c r="B2" s="41" t="s">
         <v>14</v>
@@ -1808,29 +1826,29 @@
       </c>
       <c r="J2" s="16"/>
     </row>
-    <row r="3" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="49" t="s">
+    <row r="3" spans="1:10" s="102" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="50" t="s">
+      <c r="C3" s="104" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="51">
+      <c r="D3" s="105">
         <v>0.2</v>
       </c>
-      <c r="E3" s="52">
+      <c r="E3" s="106">
         <v>46246</v>
       </c>
-      <c r="F3" s="53"/>
-      <c r="G3" s="54">
+      <c r="F3" s="107"/>
+      <c r="G3" s="108">
         <v>0.99930555555555556</v>
       </c>
-      <c r="H3" s="55" t="s">
+      <c r="H3" s="109" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="16"/>
-    </row>
-    <row r="4" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="J3" s="110"/>
+    </row>
+    <row r="4" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="56" t="s">
         <v>14</v>
       </c>
@@ -1852,7 +1870,7 @@
       </c>
       <c r="J4" s="16"/>
     </row>
-    <row r="5" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="63" t="s">
         <v>12</v>
       </c>
@@ -1874,7 +1892,7 @@
       </c>
       <c r="J5" s="16"/>
     </row>
-    <row r="6" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="64" t="s">
         <v>42</v>
       </c>
@@ -1894,7 +1912,7 @@
       <c r="H6" s="65"/>
       <c r="J6" s="16"/>
     </row>
-    <row r="7" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B7" s="66" t="s">
         <v>13</v>
       </c>
@@ -1916,7 +1934,7 @@
       </c>
       <c r="J7" s="16"/>
     </row>
-    <row r="8" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B8" s="68" t="s">
         <v>12</v>
       </c>
@@ -1935,11 +1953,8 @@
       <c r="G8" s="46"/>
       <c r="H8" s="47"/>
       <c r="J8" s="16"/>
-      <c r="K8" s="15" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="63" t="s">
         <v>12</v>
       </c>
@@ -1961,7 +1976,7 @@
       </c>
       <c r="J9" s="16"/>
     </row>
-    <row r="10" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="64" t="s">
         <v>42</v>
       </c>
@@ -1981,7 +1996,7 @@
       <c r="H10" s="65"/>
       <c r="J10" s="16"/>
     </row>
-    <row r="11" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="69" t="s">
         <v>11</v>
       </c>
@@ -2003,7 +2018,7 @@
       </c>
       <c r="J11" s="16"/>
     </row>
-    <row r="12" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B12" s="66" t="s">
         <v>13</v>
       </c>
@@ -2025,7 +2040,7 @@
       </c>
       <c r="J12" s="16"/>
     </row>
-    <row r="13" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="77"/>
       <c r="B13" s="68" t="s">
         <v>12</v>
@@ -2048,7 +2063,7 @@
       </c>
       <c r="J13" s="20"/>
     </row>
-    <row r="14" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="70" t="s">
         <v>13</v>
       </c>
@@ -2070,7 +2085,7 @@
       </c>
       <c r="J14" s="20"/>
     </row>
-    <row r="15" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B15" s="72" t="s">
         <v>42</v>
       </c>
@@ -2090,7 +2105,7 @@
       <c r="H15" s="62"/>
       <c r="J15" s="20"/>
     </row>
-    <row r="16" spans="1:11" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="49" t="s">
         <v>11</v>
       </c>
@@ -2581,121 +2596,121 @@
     <row r="1" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="78" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="78" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="D2" s="91" t="s">
         <v>60</v>
       </c>
-      <c r="D2" s="91" t="s">
+      <c r="E2" s="78" t="s">
         <v>61</v>
       </c>
-      <c r="E2" s="78" t="s">
+      <c r="F2" s="78" t="s">
         <v>62</v>
-      </c>
-      <c r="F2" s="78" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="79" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="88" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="88" t="s">
+      <c r="D3" s="93" t="s">
         <v>65</v>
       </c>
-      <c r="D3" s="93" t="s">
+      <c r="E3" s="95" t="s">
         <v>66</v>
       </c>
-      <c r="E3" s="95" t="s">
-        <v>67</v>
-      </c>
       <c r="F3" s="96" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="82" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4" s="89" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D4" s="94" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E4" s="90" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" s="101" t="s">
         <v>68</v>
-      </c>
-      <c r="F4" s="101" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="99" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="99" t="s">
+      <c r="D5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="D5" s="92" t="s">
-        <v>72</v>
-      </c>
       <c r="E5" s="93" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F5" s="86" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="80" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C6" s="100" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="84" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="84" t="s">
-        <v>72</v>
-      </c>
       <c r="E6" s="94" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F6" s="87" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="97" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C7" s="81" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D7" s="79" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E7" s="83" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F7" s="83" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="98" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C8" s="84" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="82" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="84" t="s">
         <v>73</v>
       </c>
-      <c r="D8" s="82" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8" s="84" t="s">
-        <v>74</v>
-      </c>
       <c r="F8" s="85" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/Ciclo 02 - 2026/CalendarioEvaluaciones.xlsx
+++ b/Ciclo 02 - 2026/CalendarioEvaluaciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\Ciclo 02 - 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{947F4BE0-D542-432A-B53C-C2CBAEE37E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F7056F8-C0D4-4936-9C57-5F2376F7F3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -741,7 +741,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1037,6 +1037,44 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="8" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1892,47 +1930,47 @@
       </c>
       <c r="J5" s="16"/>
     </row>
-    <row r="6" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="64" t="s">
+    <row r="6" spans="1:10" s="102" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="118" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="120">
         <v>0.1</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="121">
         <v>46251</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="122">
         <v>46257</v>
       </c>
-      <c r="G6" s="29"/>
-      <c r="H6" s="65"/>
-      <c r="J6" s="16"/>
-    </row>
-    <row r="7" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B7" s="66" t="s">
+      <c r="G6" s="123"/>
+      <c r="H6" s="124"/>
+      <c r="J6" s="110"/>
+    </row>
+    <row r="7" spans="1:10" s="102" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B7" s="111" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="57" t="s">
+      <c r="C7" s="112" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="58">
+      <c r="D7" s="113">
         <v>0.1</v>
       </c>
-      <c r="E7" s="67">
+      <c r="E7" s="114">
         <v>46253</v>
       </c>
-      <c r="F7" s="60"/>
-      <c r="G7" s="61">
+      <c r="F7" s="115"/>
+      <c r="G7" s="116">
         <v>0.79166666666666663</v>
       </c>
-      <c r="H7" s="62" t="s">
+      <c r="H7" s="117" t="s">
         <v>30</v>
       </c>
-      <c r="J7" s="16"/>
+      <c r="J7" s="110"/>
     </row>
     <row r="8" spans="1:10" s="15" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B8" s="68" t="s">

--- a/Ciclo 02 - 2026/CalendarioEvaluaciones.xlsx
+++ b/Ciclo 02 - 2026/CalendarioEvaluaciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\Ciclo 02 - 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F7056F8-C0D4-4936-9C57-5F2376F7F3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3088FAB-4973-4802-9014-CEB2D2F92E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
